--- a/docs/export-templates/AI问书_XX出版社_订单管理数据导出.xlsx
+++ b/docs/export-templates/AI问书_XX出版社_订单管理数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="94">
   <si>
     <t>机构订单管理</t>
   </si>
@@ -55,49 +55,70 @@
     <t>兑换时间</t>
   </si>
   <si>
+    <t>OD20260722100215</t>
+  </si>
+  <si>
+    <t>会员</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>¥19.9</t>
+  </si>
+  <si>
+    <t>微信支付</t>
+  </si>
+  <si>
+    <t>待支付</t>
+  </si>
+  <si>
+    <t>未退款</t>
+  </si>
+  <si>
+    <t>138****8888</t>
+  </si>
+  <si>
+    <t>2026-07-22 10:02:15</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OD20260721143050</t>
+  </si>
+  <si>
+    <t>永享</t>
+  </si>
+  <si>
+    <t>心血管分册</t>
+  </si>
+  <si>
+    <t>¥9.9</t>
+  </si>
+  <si>
+    <t>已失效</t>
+  </si>
+  <si>
+    <t>wx_abc</t>
+  </si>
+  <si>
+    <t>2026-07-21 14:30:50</t>
+  </si>
+  <si>
     <t>OD20260530152133</t>
   </si>
   <si>
-    <t>永享</t>
-  </si>
-  <si>
-    <t>心血管分册</t>
-  </si>
-  <si>
-    <t>¥9.9</t>
-  </si>
-  <si>
-    <t>微信支付</t>
-  </si>
-  <si>
     <t>已支付</t>
   </si>
   <si>
-    <t>未退款</t>
-  </si>
-  <si>
-    <t>wx_abc</t>
-  </si>
-  <si>
     <t>2026-05-30 15:21:20</t>
   </si>
   <si>
     <t>2026-05-30 15:21:33</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>OD20260530140208</t>
-  </si>
-  <si>
-    <t>会员</t>
-  </si>
-  <si>
-    <t>¥19.9</t>
-  </si>
-  <si>
-    <t>138****8888</t>
   </si>
   <si>
     <t>2026-05-30 14:01:50</t>
@@ -738,7 +759,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -863,18 +884,18 @@
         <v>23</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>27</v>
@@ -883,22 +904,22 @@
         <v>18</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -906,45 +927,45 @@
         <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="G7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="K7" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>17</v>
@@ -953,112 +974,112 @@
         <v>18</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="K10" s="7" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>20</v>
@@ -1073,7 +1094,7 @@
         <v>54</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1081,80 +1102,80 @@
         <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="J12" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="K13" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>27</v>
@@ -1163,92 +1184,92 @@
         <v>18</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="K15" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>74</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1259,92 +1280,92 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="I17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="K17" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>81</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>85</v>
@@ -1353,7 +1374,77 @@
         <v>86</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
